--- a/LubanTool/Datas/__tables__.xlsx
+++ b/LubanTool/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +122,15 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>GlobalConfigCategory</t>
+  </si>
+  <si>
+    <t>GlobalConfig</t>
+  </si>
+  <si>
+    <t>global.xlsx</t>
   </si>
   <si>
     <t>item.TbItem</t>
@@ -203,7 +212,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +223,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -676,143 +691,146 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -820,6 +838,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1144,23 +1168,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="6.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="54.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="32.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="57.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="33.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="33.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="6.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="29.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="54.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="32.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="57.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="33.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="33.375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="7.625" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:13">
@@ -1204,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,17 +1263,17 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="42.75" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="42.75" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1265,116 +1289,131 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
-      <c r="B4" s="2" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:13">
+      <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="b">
+      <c r="D4" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:13">
+      <c r="B5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2" t="b">
+      <c r="D5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:13">
+      <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="b">
+      <c r="D6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:13">
+      <c r="B7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2" t="b">
+      <c r="D7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:13">
+      <c r="B8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="b">
+      <c r="D8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:13">
+      <c r="B9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="b">
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="D10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="5" t="b">
+    <row r="11" spans="1:13">
+      <c r="B11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>50</v>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5" t="b">
+    <row r="12" spans="1:13">
+      <c r="B12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>53</v>
+      <c r="E12" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
